--- a/Table11_RoBMA_BestPractice.xlsx
+++ b/Table11_RoBMA_BestPractice.xlsx
@@ -386,17 +386,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>0.047</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[-0.002, 0.179]</t>
+          <t>[-0.071, 0.149]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[-0.375, 0.546]</t>
+          <t>[-0.437, 0.530]</t>
         </is>
       </c>
     </row>
@@ -408,17 +408,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>0.047</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[-0.002, 0.177]</t>
+          <t>[-0.071, 0.148]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[-0.359, 0.498]</t>
+          <t>[-0.411, 0.486]</t>
         </is>
       </c>
     </row>
@@ -462,17 +462,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>0.042</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[-0.023, 0.175]</t>
+          <t>[-0.083, 0.147]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[-0.391, 0.540]</t>
+          <t>[-0.449, 0.527]</t>
         </is>
       </c>
     </row>
@@ -484,17 +484,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>0.042</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[-0.023, 0.173]</t>
+          <t>[-0.083, 0.145]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[-0.372, 0.493]</t>
+          <t>[-0.421, 0.483]</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>"Best Practice" predictions are derived from the RoBMA meta-regression in Table 10. Predictions are evaluated at SC1_Cognitive = 1, LaggedDV = 0, NumberSCVars = 1, Endog_FE = 1, Reg_OECDEurope = 0, Reg_US = 0, Reg_Africa = 0, Reg_Asia = 0 (Reg_Other implied as the reference category when all four region dummies are 0). se(z) and publication year are not covariates in this model: RoBMA corrects for publication bias internally rather than through a linear se(z) term, and publication year was not retained by the BIC pre-selection in Table 9.</t>
+          <t>"Best Practice" predictions are derived from the RoBMA meta-regression in Table 10. Predictions are evaluated at Endog_FE = 1, Reg_OECDEurope = 0 (the reference category -- combining Reg_US, Reg_Africa, Reg_Asia, and Reg_Other -- is implied when Reg_OECDEurope = 0). se(z) and publication year are not covariates in this model: RoBMA corrects for publication bias internally rather than through a linear se(z) term, and publication year was not retained by the BIC pre-selection in Table 9. No other moderator is retained by that pre-selection, so the model conditions on Endog_FE and Reg_OECDEurope only (see the Decision point following Table 10).</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>"Best Practice" predictions are derived from the RoBMA meta-regression in Table 10. Predictions are evaluated at SC1_Cognitive = 1, LaggedDV = 0, NumberSCVars = 1, Endog_FE = 1, Reg_OECDEurope = 1, Reg_US = 0, Reg_Africa = 0, Reg_Asia = 0 (Reg_Other implied as the reference category when all four region dummies are 0). se(z) and publication year are not covariates in this model: RoBMA corrects for publication bias internally rather than through a linear se(z) term, and publication year was not retained by the BIC pre-selection in Table 9.</t>
+          <t>"Best Practice" predictions are derived from the RoBMA meta-regression in Table 10. Predictions are evaluated at Endog_FE = 1, Reg_OECDEurope = 1 (the reference category -- combining Reg_US, Reg_Africa, Reg_Asia, and Reg_Other -- is implied when Reg_OECDEurope = 0). se(z) and publication year are not covariates in this model: RoBMA corrects for publication bias internally rather than through a linear se(z) term, and publication year was not retained by the BIC pre-selection in Table 9. No other moderator is retained by that pre-selection, so the model conditions on Endog_FE and Reg_OECDEurope only (see the Decision point following Table 10).</t>
         </is>
       </c>
     </row>

--- a/Table11_RoBMA_BestPractice.xlsx
+++ b/Table11_RoBMA_BestPractice.xlsx
@@ -386,17 +386,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>0.053</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[-0.071, 0.149]</t>
+          <t>[-0.027, 0.144]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[-0.437, 0.530]</t>
+          <t>[-0.423, 0.528]</t>
         </is>
       </c>
     </row>
@@ -408,17 +408,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>0.053</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[-0.071, 0.148]</t>
+          <t>[-0.027, 0.143]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[-0.411, 0.486]</t>
+          <t>[-0.399, 0.484]</t>
         </is>
       </c>
     </row>
@@ -462,17 +462,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>0.046</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[-0.083, 0.147]</t>
+          <t>[-0.046, 0.141]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[-0.449, 0.527]</t>
+          <t>[-0.431, 0.525]</t>
         </is>
       </c>
     </row>
@@ -484,17 +484,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>0.046</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[-0.083, 0.145]</t>
+          <t>[-0.046, 0.140]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[-0.421, 0.483]</t>
+          <t>[-0.406, 0.481]</t>
         </is>
       </c>
     </row>
